--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260519_211101.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260519_211101.xlsx
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260519_211101.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260519_211101.xlsx
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
